--- a/data/median_living_standard/Niveau_de_vie_median_2017.xlsx
+++ b/data/median_living_standard/Niveau_de_vie_median_2017.xlsx
@@ -262,9 +262,15 @@
     <t>Aude</t>
   </si>
   <si>
+    <t>2A</t>
+  </si>
+  <si>
     <t>Corse-du-Sud</t>
   </si>
   <si>
+    <t>2B</t>
+  </si>
+  <si>
     <t>Haute-Corse</t>
   </si>
   <si>
@@ -304,13 +310,7 @@
     <t>Val-d'Oise</t>
   </si>
   <si>
-    <t>2A</t>
-  </si>
-  <si>
     <t>Seine-Saint-Denis</t>
-  </si>
-  <si>
-    <t>2B</t>
   </si>
   <si>
     <t>Meuse</t>
@@ -733,7 +733,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="16.5">
       <c r="A2" s="4">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -744,7 +744,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="16.5">
       <c r="A3" s="4">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -755,7 +755,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="16.5">
       <c r="A4" s="4">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -766,7 +766,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="16.5">
       <c r="A5" s="4">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -777,7 +777,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="16.5">
       <c r="A6" s="4">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
@@ -788,7 +788,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="16.5">
       <c r="A7" s="4">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -799,7 +799,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="16.5">
       <c r="A8" s="4">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
@@ -810,7 +810,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="16.5">
       <c r="A9" s="4">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -821,7 +821,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="16.5">
       <c r="A10" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
@@ -832,7 +832,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="16.5">
       <c r="A11" s="4">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -843,7 +843,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="16.5">
       <c r="A12" s="4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
@@ -854,7 +854,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="16.5">
       <c r="A13" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -865,7 +865,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="16.5">
       <c r="A14" s="4">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -876,7 +876,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="16.5">
       <c r="A15" s="4">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -887,7 +887,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="16.5">
       <c r="A16" s="4">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
@@ -898,7 +898,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="16.5">
       <c r="A17" s="4">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
@@ -909,7 +909,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="16.5">
       <c r="A18" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -920,7 +920,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="16.5">
       <c r="A19" s="4">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -931,7 +931,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="16.5">
       <c r="A20" s="4">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -942,7 +942,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="16.5">
       <c r="A21" s="4">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -953,7 +953,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="16.5">
       <c r="A22" s="4">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -964,7 +964,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="16.5">
       <c r="A23" s="4">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -975,7 +975,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="16.5">
       <c r="A24" s="4">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -986,7 +986,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="16.5">
       <c r="A25" s="4">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -997,7 +997,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="16.5">
       <c r="A26" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="16.5">
       <c r="A27" s="4">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="16.5">
       <c r="A28" s="4">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="16.5">
       <c r="A29" s="4">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="16.5">
       <c r="A30" s="4">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="16.5">
       <c r="A31" s="4">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="16.5">
       <c r="A32" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="16.5">
       <c r="A33" s="4">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="16.5">
       <c r="A34" s="4">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="16.5">
       <c r="A35" s="4">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="16.5">
       <c r="A36" s="4">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
@@ -1118,7 +1118,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="16.5">
       <c r="A37" s="4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>38</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="16.5">
       <c r="A38" s="4">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
@@ -1140,7 +1140,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="16.5">
       <c r="A39" s="4">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
@@ -1151,7 +1151,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="16.5">
       <c r="A40" s="4">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="16.5">
       <c r="A41" s="4">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>42</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="16.5">
       <c r="A42" s="4">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="16.5">
       <c r="A43" s="4">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="16.5">
       <c r="A44" s="4">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>45</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="16.5">
       <c r="A45" s="4">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>46</v>
@@ -1217,7 +1217,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="16.5">
       <c r="A46" s="4">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="16.5">
       <c r="A47" s="4">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>48</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="16.5">
       <c r="A48" s="4">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="16.5">
       <c r="A49" s="4">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>50</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="16.5">
       <c r="A50" s="4">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>51</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="16.5">
       <c r="A51" s="4">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>52</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="16.5">
       <c r="A52" s="4">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>53</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="16.5">
       <c r="A53" s="4">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>54</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="16.5">
       <c r="A54" s="4">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>55</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="16.5">
       <c r="A55" s="4">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>56</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="16.5">
       <c r="A56" s="4">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>57</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="16.5">
       <c r="A57" s="4">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>58</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="16.5">
       <c r="A58" s="4">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>59</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="16.5">
       <c r="A59" s="4">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>60</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="16.5">
       <c r="A60" s="4">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>61</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="16.5">
       <c r="A61" s="4">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>62</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="16.5">
       <c r="A62" s="4">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="16.5">
       <c r="A63" s="4">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>64</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="16.5">
       <c r="A64" s="4">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>65</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="16.5">
       <c r="A65" s="4">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>66</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="16.5">
       <c r="A66" s="4">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>67</v>
@@ -1448,7 +1448,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="16.5">
       <c r="A67" s="4">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>68</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="16.5">
       <c r="A68" s="4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>69</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="16.5">
       <c r="A69" s="4">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>70</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="16.5">
       <c r="A70" s="4">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>71</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="16.5">
       <c r="A71" s="4">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>72</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="16.5">
       <c r="A72" s="4">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>73</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="16.5">
       <c r="A73" s="4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>74</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="16.5">
       <c r="A74" s="4">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>75</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="16.5">
       <c r="A75" s="4">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="16.5">
       <c r="A76" s="4">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>77</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="16.5">
       <c r="A77" s="4">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="16.5">
       <c r="A78" s="4">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>79</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="16.5">
       <c r="A79" s="4">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>80</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="16.5">
       <c r="A80" s="4">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>81</v>
@@ -1601,22 +1601,22 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="16.5">
-      <c r="A81" s="4">
-        <v>81</v>
+      <c r="A81" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C81" s="5">
         <v>20860</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="16.5">
-      <c r="A82" s="4">
-        <v>82</v>
+      <c r="A82" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C82" s="5">
         <v>19260</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="16.5">
       <c r="A83" s="4">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C83" s="5">
         <v>21500</v>
@@ -1635,10 +1635,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="16.5">
       <c r="A84" s="4">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C84" s="5">
         <v>19720</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="16.5">
       <c r="A85" s="4">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C85" s="5">
         <v>19490</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="16.5">
       <c r="A86" s="4">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C86" s="5">
         <v>19100</v>
@@ -1668,10 +1668,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="16.5">
       <c r="A87" s="4">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C87" s="5">
         <v>18610</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="16.5">
       <c r="A88" s="4">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C88" s="5">
         <v>27420</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="16.5">
       <c r="A89" s="4">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C89" s="5">
         <v>27090</v>
@@ -1701,10 +1701,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="16.5">
       <c r="A90" s="4">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C90" s="5">
         <v>26130</v>
@@ -1715,7 +1715,7 @@
         <v>91</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C91" s="5">
         <v>23360</v>
@@ -1723,10 +1723,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="16.5">
       <c r="A92" s="4">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C92" s="5">
         <v>22820</v>
@@ -1737,7 +1737,7 @@
         <v>94</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C93" s="5">
         <v>22920</v>
@@ -1748,26 +1748,26 @@
         <v>95</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C94" s="5">
         <v>21470</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="16.5">
-      <c r="A95" s="1" t="s">
-        <v>96</v>
+      <c r="A95" s="4">
+        <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C95" s="5">
         <v>17310</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="16.5">
-      <c r="A96" s="1" t="s">
-        <v>98</v>
+      <c r="A96" s="4">
+        <v>55</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>99</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="16.5">
       <c r="A97" s="4">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>100</v>
